--- a/output/pdf_financials_xlsx/ITH.xlsx
+++ b/output/pdf_financials_xlsx/ITH.xlsx
@@ -879,40 +879,40 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.183253</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.103759</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.05667</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.04367</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.01749</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.027395</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.119106</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.164533</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.005739</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.097126</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.083936</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.073755</v>
       </c>
     </row>
     <row r="13">
@@ -1626,40 +1626,40 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-56.643462</v>
+        <v>-56.826715</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-9.85248</v>
+        <v>-9.956239</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-7.767096</v>
+        <v>-7.823766</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.812824</v>
+        <v>-4.856494</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-7.190628</v>
+        <v>-7.208118</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-6.432057</v>
+        <v>-6.459452</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-4.192038</v>
+        <v>-4.311144</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-3.826407</v>
+        <v>-3.99094</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-3.041693</v>
+        <v>-3.047432</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-3.397969</v>
+        <v>-3.495095</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-3.599372</v>
+        <v>-3.683308</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-4.638333</v>
+        <v>-4.712088</v>
       </c>
     </row>
     <row r="28">
@@ -1712,40 +1712,40 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-56.611802</v>
+        <v>-56.795055</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-9.830679999999999</v>
+        <v>-9.934438999999999</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-7.751317</v>
+        <v>-7.807987</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.805777</v>
+        <v>-4.849447</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-7.185345</v>
+        <v>-7.202835</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-6.428051</v>
+        <v>-6.455446</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-4.188995</v>
+        <v>-4.308101</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-3.824091</v>
+        <v>-3.988624</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-3.041693</v>
+        <v>-3.047432</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-3.397969</v>
+        <v>-3.495095</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-3.599372</v>
+        <v>-3.683308</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-4.638333</v>
+        <v>-4.712088</v>
       </c>
     </row>
     <row r="30">
@@ -15322,7 +15322,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
